--- a/04-进度督察/节点汇总/土建完成节点汇总v2_20260805.xlsx
+++ b/04-进度督察/节点汇总/土建完成节点汇总v2_20260805.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\重大节点进度追踪通报及存档汇总\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrseven\Desktop\总经办文档\04-进度督察\节点汇总\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -720,7 +720,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,12 +736,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,7 +1062,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1092,16 +1086,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1110,89 +1104,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1213,9 +1207,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1608,8 +1599,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.83333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.8333333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="55.0833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.8333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.8333333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="8.83333333333333" style="3" customWidth="1"/>
@@ -2727,25 +2718,25 @@
       <c r="A55" s="7">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="7">
         <v>10</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H55" s="7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2773,25 +2764,25 @@
       <c r="A57" s="7">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="7">
         <v>10</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2894,7 +2885,7 @@
       <c r="F62" s="7">
         <v>5</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="8" t="s">
         <v>86</v>
       </c>
       <c r="H62" s="7" t="s">
@@ -2940,7 +2931,7 @@
       <c r="F64" s="7">
         <v>5</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="8" t="s">
         <v>86</v>
       </c>
       <c r="H64" s="7" t="s">
@@ -4354,7 +4345,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C1:F1 A1 A2:F31 A32:B32 D32:F32 A33:F34 A35:B35 D35:F35 A36:F54 A55:B55 D55:F55 A56:F61 A62:B62 D62:F62 A63:F63 A64:B64 D64:F64 A65:F134" numberStoredAsText="1"/>
+    <ignoredError sqref="A65:F134 D64:F64 A64:B64 A63:F63 D62:F62 A62:B62 A56:F61 D55:F55 A55:B55 A36:F54 D35:F35 A35:B35 A33:F34 D32:F32 A32:B32 A2:F31 A1 C1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>